--- a/Sample_run/1/student/linhmndhe186854/OverallSummary.xlsx
+++ b/Sample_run/1/student/linhmndhe186854/OverallSummary.xlsx
@@ -64,7 +64,7 @@
     <x:t>TC6</x:t>
   </x:si>
   <x:si>
-    <x:t>Network flows: 20 FAIL (ALL-OR-NOTHING), 2 PASS</x:t>
+    <x:t>The operation was canceled.</x:t>
   </x:si>
 </x:sst>
 </file>
